--- a/output_to.xlsx
+++ b/output_to.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="1694">
   <si>
     <t>SL.No</t>
     <phoneticPr fontId="1"/>
@@ -1729,6 +1729,4782 @@
   </si>
   <si>
     <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SL.No</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Flt No.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep FltNo.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Regn No.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Origin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dest</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr StdTyp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep Time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep StdTyp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MTOW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Landing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Normal HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Double HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Remote HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Parking</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SL.No</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Flt No.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep FltNo.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Regn No.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Origin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dest</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr StdTyp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep Time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep StdTyp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MTOW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Landing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Normal HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Double HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Remote HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Parking</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SL.No</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Flt No.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep FltNo.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Regn No.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Origin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dest</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr StdTyp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep Time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep StdTyp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MTOW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Landing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Normal HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Double HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Remote HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Parking</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2297,63 +7073,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" t="s" s="1">
-        <v>268</v>
+        <v>1225</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>269</v>
+        <v>1226</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>270</v>
+        <v>1227</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>271</v>
+        <v>1228</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>272</v>
+        <v>1229</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>273</v>
+        <v>1230</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>274</v>
+        <v>1231</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>275</v>
+        <v>1232</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>276</v>
+        <v>1233</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>277</v>
+        <v>1234</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>278</v>
+        <v>1235</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>279</v>
+        <v>1236</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>280</v>
+        <v>1237</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>281</v>
+        <v>1238</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>282</v>
+        <v>1239</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>283</v>
+        <v>1240</v>
       </c>
       <c r="Q1" t="s" s="3">
-        <v>284</v>
+        <v>1241</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>285</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2361,37 +7137,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>286</v>
+        <v>1243</v>
       </c>
       <c r="C2" t="s">
-        <v>287</v>
+        <v>1244</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>288</v>
+        <v>1245</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>1246</v>
       </c>
       <c r="F2" t="s">
-        <v>290</v>
+        <v>1247</v>
       </c>
       <c r="G2" t="s" s="3">
-        <v>291</v>
+        <v>1248</v>
       </c>
       <c r="H2" t="s">
-        <v>292</v>
+        <v>1249</v>
       </c>
       <c r="I2" t="s">
-        <v>293</v>
+        <v>1250</v>
       </c>
       <c r="J2" t="s" s="3">
-        <v>294</v>
+        <v>1251</v>
       </c>
       <c r="K2" t="s">
-        <v>295</v>
+        <v>1252</v>
       </c>
       <c r="L2" t="s">
-        <v>296</v>
+        <v>1253</v>
       </c>
       <c r="M2" s="3">
         <v>79</v>
@@ -2409,7 +7185,7 @@
         <v>6</v>
       </c>
       <c r="R2" t="s">
-        <v>297</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2417,37 +7193,37 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>298</v>
+        <v>1255</v>
       </c>
       <c r="C3" t="s">
-        <v>299</v>
+        <v>1256</v>
       </c>
       <c r="D3" t="s" s="3">
-        <v>300</v>
+        <v>1257</v>
       </c>
       <c r="E3" t="s">
-        <v>301</v>
+        <v>1258</v>
       </c>
       <c r="F3" t="s">
-        <v>302</v>
+        <v>1259</v>
       </c>
       <c r="G3" t="s" s="3">
-        <v>303</v>
+        <v>1260</v>
       </c>
       <c r="H3" t="s">
-        <v>304</v>
+        <v>1261</v>
       </c>
       <c r="I3" t="s">
-        <v>305</v>
+        <v>1262</v>
       </c>
       <c r="J3" t="s" s="3">
-        <v>306</v>
+        <v>1263</v>
       </c>
       <c r="K3" t="s">
-        <v>307</v>
+        <v>1264</v>
       </c>
       <c r="L3" t="s">
-        <v>308</v>
+        <v>1265</v>
       </c>
       <c r="M3" s="3">
         <v>77</v>
@@ -2465,7 +7241,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>309</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2473,37 +7249,37 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>310</v>
+        <v>1267</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
+        <v>1268</v>
       </c>
       <c r="D4" t="s" s="3">
-        <v>312</v>
+        <v>1269</v>
       </c>
       <c r="E4" t="s">
-        <v>313</v>
+        <v>1270</v>
       </c>
       <c r="F4" t="s">
-        <v>314</v>
+        <v>1271</v>
       </c>
       <c r="G4" t="s" s="3">
-        <v>315</v>
+        <v>1272</v>
       </c>
       <c r="H4" t="s">
-        <v>316</v>
+        <v>1273</v>
       </c>
       <c r="I4" t="s">
-        <v>317</v>
+        <v>1274</v>
       </c>
       <c r="J4" t="s" s="3">
-        <v>318</v>
+        <v>1275</v>
       </c>
       <c r="K4" t="s">
-        <v>319</v>
+        <v>1276</v>
       </c>
       <c r="L4" t="s">
-        <v>320</v>
+        <v>1277</v>
       </c>
       <c r="M4" s="3">
         <v>89</v>
@@ -2529,37 +7305,37 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>321</v>
+        <v>1278</v>
       </c>
       <c r="C5" t="s">
-        <v>322</v>
+        <v>1279</v>
       </c>
       <c r="D5" t="s" s="3">
-        <v>323</v>
+        <v>1280</v>
       </c>
       <c r="E5" t="s">
-        <v>324</v>
+        <v>1281</v>
       </c>
       <c r="F5" t="s">
-        <v>325</v>
+        <v>1282</v>
       </c>
       <c r="G5" t="s" s="3">
-        <v>326</v>
+        <v>1283</v>
       </c>
       <c r="H5" t="s">
-        <v>327</v>
+        <v>1284</v>
       </c>
       <c r="I5" t="s">
-        <v>328</v>
+        <v>1285</v>
       </c>
       <c r="J5" t="s" s="3">
-        <v>329</v>
+        <v>1286</v>
       </c>
       <c r="K5" t="s">
-        <v>330</v>
+        <v>1287</v>
       </c>
       <c r="L5" t="s">
-        <v>331</v>
+        <v>1288</v>
       </c>
       <c r="M5" s="3">
         <v>23</v>
@@ -2577,7 +7353,7 @@
         <v>13</v>
       </c>
       <c r="R5" t="s">
-        <v>332</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -2585,37 +7361,37 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>1290</v>
       </c>
       <c r="C6" t="s">
-        <v>334</v>
+        <v>1291</v>
       </c>
       <c r="D6" t="s">
-        <v>335</v>
+        <v>1292</v>
       </c>
       <c r="E6" t="s">
-        <v>336</v>
+        <v>1293</v>
       </c>
       <c r="F6" t="s">
-        <v>337</v>
+        <v>1294</v>
       </c>
       <c r="G6" t="s">
-        <v>338</v>
+        <v>1295</v>
       </c>
       <c r="H6" t="s">
-        <v>339</v>
+        <v>1296</v>
       </c>
       <c r="I6" t="s">
-        <v>340</v>
+        <v>1297</v>
       </c>
       <c r="J6" t="s">
-        <v>341</v>
+        <v>1298</v>
       </c>
       <c r="K6" t="s">
-        <v>342</v>
+        <v>1299</v>
       </c>
       <c r="L6" t="s">
-        <v>343</v>
+        <v>1300</v>
       </c>
       <c r="M6">
         <v>23</v>
@@ -2633,7 +7409,7 @@
         <v>10</v>
       </c>
       <c r="R6" t="s">
-        <v>344</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -2641,37 +7417,37 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>345</v>
+        <v>1302</v>
       </c>
       <c r="C7" t="s">
-        <v>346</v>
+        <v>1303</v>
       </c>
       <c r="D7" t="s">
-        <v>347</v>
+        <v>1304</v>
       </c>
       <c r="E7" t="s">
-        <v>348</v>
+        <v>1305</v>
       </c>
       <c r="F7" t="s">
-        <v>349</v>
+        <v>1306</v>
       </c>
       <c r="G7" t="s">
-        <v>350</v>
+        <v>1307</v>
       </c>
       <c r="H7" t="s">
-        <v>351</v>
+        <v>1308</v>
       </c>
       <c r="I7" t="s">
-        <v>352</v>
+        <v>1309</v>
       </c>
       <c r="J7" t="s">
-        <v>353</v>
+        <v>1310</v>
       </c>
       <c r="K7" t="s">
-        <v>354</v>
+        <v>1311</v>
       </c>
       <c r="L7" t="s">
-        <v>355</v>
+        <v>1312</v>
       </c>
       <c r="M7">
         <v>79</v>
@@ -2689,7 +7465,7 @@
         <v>8</v>
       </c>
       <c r="R7" t="s">
-        <v>356</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2697,37 +7473,37 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>357</v>
+        <v>1314</v>
       </c>
       <c r="C8" t="s">
-        <v>358</v>
+        <v>1315</v>
       </c>
       <c r="D8" t="s">
-        <v>359</v>
+        <v>1316</v>
       </c>
       <c r="E8" t="s">
-        <v>360</v>
+        <v>1317</v>
       </c>
       <c r="F8" t="s">
-        <v>361</v>
+        <v>1318</v>
       </c>
       <c r="G8" t="s">
-        <v>362</v>
+        <v>1319</v>
       </c>
       <c r="H8" t="s">
-        <v>363</v>
+        <v>1320</v>
       </c>
       <c r="I8" t="s">
-        <v>364</v>
+        <v>1321</v>
       </c>
       <c r="J8" t="s">
-        <v>365</v>
+        <v>1322</v>
       </c>
       <c r="K8" t="s">
-        <v>366</v>
+        <v>1323</v>
       </c>
       <c r="L8" t="s">
-        <v>367</v>
+        <v>1324</v>
       </c>
       <c r="M8">
         <v>77</v>
@@ -2745,7 +7521,7 @@
         <v>32</v>
       </c>
       <c r="R8" t="s">
-        <v>368</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -2753,37 +7529,37 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>369</v>
+        <v>1326</v>
       </c>
       <c r="C9" t="s">
-        <v>370</v>
+        <v>1327</v>
       </c>
       <c r="D9" t="s">
-        <v>371</v>
+        <v>1328</v>
       </c>
       <c r="E9" t="s">
-        <v>372</v>
+        <v>1329</v>
       </c>
       <c r="F9" t="s">
-        <v>373</v>
+        <v>1330</v>
       </c>
       <c r="G9" t="s">
-        <v>374</v>
+        <v>1331</v>
       </c>
       <c r="H9" t="s">
-        <v>375</v>
+        <v>1332</v>
       </c>
       <c r="I9" t="s">
-        <v>376</v>
+        <v>1333</v>
       </c>
       <c r="J9" t="s">
-        <v>377</v>
+        <v>1334</v>
       </c>
       <c r="K9" t="s">
-        <v>378</v>
+        <v>1335</v>
       </c>
       <c r="L9" t="s">
-        <v>379</v>
+        <v>1336</v>
       </c>
       <c r="M9">
         <v>77</v>
@@ -2801,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>380</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -2809,37 +7585,37 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>381</v>
+        <v>1338</v>
       </c>
       <c r="C10" t="s">
-        <v>382</v>
+        <v>1339</v>
       </c>
       <c r="D10" t="s">
-        <v>383</v>
+        <v>1340</v>
       </c>
       <c r="E10" t="s">
-        <v>384</v>
+        <v>1341</v>
       </c>
       <c r="F10" t="s">
-        <v>385</v>
+        <v>1342</v>
       </c>
       <c r="G10" t="s">
-        <v>386</v>
+        <v>1343</v>
       </c>
       <c r="H10" t="s">
-        <v>387</v>
+        <v>1344</v>
       </c>
       <c r="I10" t="s">
-        <v>388</v>
+        <v>1345</v>
       </c>
       <c r="J10" t="s">
-        <v>389</v>
+        <v>1346</v>
       </c>
       <c r="K10" t="s">
-        <v>390</v>
+        <v>1347</v>
       </c>
       <c r="L10" t="s">
-        <v>391</v>
+        <v>1348</v>
       </c>
       <c r="M10">
         <v>77</v>
@@ -2857,7 +7633,7 @@
         <v>32</v>
       </c>
       <c r="R10" t="s">
-        <v>392</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2865,37 +7641,37 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>393</v>
+        <v>1350</v>
       </c>
       <c r="C11" t="s">
-        <v>394</v>
+        <v>1351</v>
       </c>
       <c r="D11" t="s">
-        <v>395</v>
+        <v>1352</v>
       </c>
       <c r="E11" t="s">
-        <v>396</v>
+        <v>1353</v>
       </c>
       <c r="F11" t="s">
-        <v>397</v>
+        <v>1354</v>
       </c>
       <c r="G11" t="s">
-        <v>398</v>
+        <v>1355</v>
       </c>
       <c r="H11" t="s">
-        <v>399</v>
+        <v>1356</v>
       </c>
       <c r="I11" t="s">
-        <v>400</v>
+        <v>1357</v>
       </c>
       <c r="J11" t="s">
-        <v>401</v>
+        <v>1358</v>
       </c>
       <c r="K11" t="s">
-        <v>402</v>
+        <v>1359</v>
       </c>
       <c r="L11" t="s">
-        <v>403</v>
+        <v>1360</v>
       </c>
       <c r="M11">
         <v>77</v>
@@ -2913,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>404</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2921,37 +7697,37 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>405</v>
+        <v>1362</v>
       </c>
       <c r="C12" t="s">
-        <v>406</v>
+        <v>1363</v>
       </c>
       <c r="D12" t="s">
-        <v>407</v>
+        <v>1364</v>
       </c>
       <c r="E12" t="s">
-        <v>408</v>
+        <v>1365</v>
       </c>
       <c r="F12" t="s">
-        <v>409</v>
+        <v>1366</v>
       </c>
       <c r="G12" t="s">
-        <v>410</v>
+        <v>1367</v>
       </c>
       <c r="H12" t="s">
-        <v>411</v>
+        <v>1368</v>
       </c>
       <c r="I12" t="s">
-        <v>412</v>
+        <v>1369</v>
       </c>
       <c r="J12" t="s">
-        <v>413</v>
+        <v>1370</v>
       </c>
       <c r="K12" t="s">
-        <v>414</v>
+        <v>1371</v>
       </c>
       <c r="L12" t="s">
-        <v>415</v>
+        <v>1372</v>
       </c>
       <c r="M12">
         <v>77</v>
@@ -2969,7 +7745,7 @@
         <v>32</v>
       </c>
       <c r="R12" t="s">
-        <v>416</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2977,37 +7753,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>417</v>
+        <v>1374</v>
       </c>
       <c r="C13" t="s">
-        <v>418</v>
+        <v>1375</v>
       </c>
       <c r="D13" t="s">
-        <v>419</v>
+        <v>1376</v>
       </c>
       <c r="E13" t="s">
-        <v>420</v>
+        <v>1377</v>
       </c>
       <c r="F13" t="s">
-        <v>421</v>
+        <v>1378</v>
       </c>
       <c r="G13" t="s">
-        <v>422</v>
+        <v>1379</v>
       </c>
       <c r="H13" t="s">
-        <v>423</v>
+        <v>1380</v>
       </c>
       <c r="I13" t="s">
-        <v>424</v>
+        <v>1381</v>
       </c>
       <c r="J13" t="s">
-        <v>425</v>
+        <v>1382</v>
       </c>
       <c r="K13" t="s">
-        <v>426</v>
+        <v>1383</v>
       </c>
       <c r="L13" t="s">
-        <v>427</v>
+        <v>1384</v>
       </c>
       <c r="M13">
         <v>77</v>
@@ -3025,7 +7801,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>428</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -3033,37 +7809,37 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>429</v>
+        <v>1386</v>
       </c>
       <c r="C14" t="s">
-        <v>430</v>
+        <v>1387</v>
       </c>
       <c r="D14" t="s">
-        <v>431</v>
+        <v>1388</v>
       </c>
       <c r="E14" t="s">
-        <v>432</v>
+        <v>1389</v>
       </c>
       <c r="F14" t="s">
-        <v>433</v>
+        <v>1390</v>
       </c>
       <c r="G14" t="s">
-        <v>434</v>
+        <v>1391</v>
       </c>
       <c r="H14" t="s">
-        <v>435</v>
+        <v>1392</v>
       </c>
       <c r="I14" t="s">
-        <v>436</v>
+        <v>1393</v>
       </c>
       <c r="J14" t="s">
-        <v>437</v>
+        <v>1394</v>
       </c>
       <c r="K14" t="s">
-        <v>438</v>
+        <v>1395</v>
       </c>
       <c r="L14" t="s">
-        <v>439</v>
+        <v>1396</v>
       </c>
       <c r="M14">
         <v>79</v>
@@ -3081,7 +7857,7 @@
         <v>6</v>
       </c>
       <c r="R14" t="s">
-        <v>440</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -3089,37 +7865,37 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>441</v>
+        <v>1398</v>
       </c>
       <c r="C15" t="s">
-        <v>442</v>
+        <v>1399</v>
       </c>
       <c r="D15" t="s">
-        <v>443</v>
+        <v>1400</v>
       </c>
       <c r="E15" t="s">
-        <v>444</v>
+        <v>1401</v>
       </c>
       <c r="F15" t="s">
-        <v>445</v>
+        <v>1402</v>
       </c>
       <c r="G15" t="s">
-        <v>446</v>
+        <v>1403</v>
       </c>
       <c r="H15" t="s">
-        <v>447</v>
+        <v>1404</v>
       </c>
       <c r="I15" t="s">
-        <v>448</v>
+        <v>1405</v>
       </c>
       <c r="J15" t="s">
-        <v>449</v>
+        <v>1406</v>
       </c>
       <c r="K15" t="s">
-        <v>450</v>
+        <v>1407</v>
       </c>
       <c r="L15" t="s">
-        <v>451</v>
+        <v>1408</v>
       </c>
       <c r="M15">
         <v>77</v>
@@ -3137,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>452</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -3145,37 +7921,37 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>453</v>
+        <v>1410</v>
       </c>
       <c r="C16" t="s">
-        <v>454</v>
+        <v>1411</v>
       </c>
       <c r="D16" t="s">
-        <v>455</v>
+        <v>1412</v>
       </c>
       <c r="E16" t="s">
-        <v>456</v>
+        <v>1413</v>
       </c>
       <c r="F16" t="s">
-        <v>457</v>
+        <v>1414</v>
       </c>
       <c r="G16" t="s">
-        <v>458</v>
+        <v>1415</v>
       </c>
       <c r="H16" t="s">
-        <v>459</v>
+        <v>1416</v>
       </c>
       <c r="I16" t="s">
-        <v>460</v>
+        <v>1417</v>
       </c>
       <c r="J16" t="s">
-        <v>461</v>
+        <v>1418</v>
       </c>
       <c r="K16" t="s">
-        <v>462</v>
+        <v>1419</v>
       </c>
       <c r="L16" t="s">
-        <v>463</v>
+        <v>1420</v>
       </c>
       <c r="M16">
         <v>89</v>
@@ -3201,37 +7977,37 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>464</v>
+        <v>1421</v>
       </c>
       <c r="C17" t="s">
-        <v>465</v>
+        <v>1422</v>
       </c>
       <c r="D17" t="s">
-        <v>466</v>
+        <v>1423</v>
       </c>
       <c r="E17" t="s">
-        <v>467</v>
+        <v>1424</v>
       </c>
       <c r="F17" t="s">
-        <v>468</v>
+        <v>1425</v>
       </c>
       <c r="G17" t="s">
-        <v>469</v>
+        <v>1426</v>
       </c>
       <c r="H17" t="s">
-        <v>470</v>
+        <v>1427</v>
       </c>
       <c r="I17" t="s">
-        <v>471</v>
+        <v>1428</v>
       </c>
       <c r="J17" t="s">
-        <v>472</v>
+        <v>1429</v>
       </c>
       <c r="K17" t="s">
-        <v>473</v>
+        <v>1430</v>
       </c>
       <c r="L17" t="s">
-        <v>474</v>
+        <v>1431</v>
       </c>
       <c r="M17">
         <v>23</v>
@@ -3249,7 +8025,7 @@
         <v>13</v>
       </c>
       <c r="R17" t="s">
-        <v>475</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -3257,37 +8033,37 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>476</v>
+        <v>1433</v>
       </c>
       <c r="C18" t="s">
-        <v>477</v>
+        <v>1434</v>
       </c>
       <c r="D18" t="s">
-        <v>478</v>
+        <v>1435</v>
       </c>
       <c r="E18" t="s">
-        <v>479</v>
+        <v>1436</v>
       </c>
       <c r="F18" t="s">
-        <v>480</v>
+        <v>1437</v>
       </c>
       <c r="G18" t="s">
-        <v>481</v>
+        <v>1438</v>
       </c>
       <c r="H18" t="s">
-        <v>482</v>
+        <v>1439</v>
       </c>
       <c r="I18" t="s">
-        <v>483</v>
+        <v>1440</v>
       </c>
       <c r="J18" t="s">
-        <v>484</v>
+        <v>1441</v>
       </c>
       <c r="K18" t="s">
-        <v>485</v>
+        <v>1442</v>
       </c>
       <c r="L18" t="s">
-        <v>486</v>
+        <v>1443</v>
       </c>
       <c r="M18">
         <v>23</v>
@@ -3305,7 +8081,7 @@
         <v>10</v>
       </c>
       <c r="R18" t="s">
-        <v>487</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -3313,37 +8089,37 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>488</v>
+        <v>1445</v>
       </c>
       <c r="C19" t="s">
-        <v>489</v>
+        <v>1446</v>
       </c>
       <c r="D19" t="s">
-        <v>490</v>
+        <v>1447</v>
       </c>
       <c r="E19" t="s">
-        <v>491</v>
+        <v>1448</v>
       </c>
       <c r="F19" t="s">
-        <v>492</v>
+        <v>1449</v>
       </c>
       <c r="G19" t="s">
-        <v>493</v>
+        <v>1450</v>
       </c>
       <c r="H19" t="s">
-        <v>494</v>
+        <v>1451</v>
       </c>
       <c r="I19" t="s">
-        <v>495</v>
+        <v>1452</v>
       </c>
       <c r="J19" t="s">
-        <v>496</v>
+        <v>1453</v>
       </c>
       <c r="K19" t="s">
-        <v>497</v>
+        <v>1454</v>
       </c>
       <c r="L19" t="s">
-        <v>498</v>
+        <v>1455</v>
       </c>
       <c r="M19">
         <v>79</v>
@@ -3361,11 +8137,1131 @@
         <v>8</v>
       </c>
       <c r="R19" t="s">
-        <v>499</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="21" spans="6:6">
       <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1462</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1463</v>
+      </c>
+      <c r="I22" t="s">
+        <v>1464</v>
+      </c>
+      <c r="J22" t="s">
+        <v>1465</v>
+      </c>
+      <c r="K22" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L22" t="s">
+        <v>1467</v>
+      </c>
+      <c r="M22">
+        <v>77</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>2</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>32</v>
+      </c>
+      <c r="R22" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1474</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1475</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1476</v>
+      </c>
+      <c r="J23" t="s">
+        <v>1477</v>
+      </c>
+      <c r="K23" t="s">
+        <v>1478</v>
+      </c>
+      <c r="L23" t="s">
+        <v>1479</v>
+      </c>
+      <c r="M23">
+        <v>77</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>2</v>
+      </c>
+      <c r="P23">
+        <v>3</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1486</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1487</v>
+      </c>
+      <c r="I24" t="s">
+        <v>1488</v>
+      </c>
+      <c r="J24" t="s">
+        <v>1489</v>
+      </c>
+      <c r="K24" t="s">
+        <v>1490</v>
+      </c>
+      <c r="L24" t="s">
+        <v>1491</v>
+      </c>
+      <c r="M24">
+        <v>79</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>2</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>6</v>
+      </c>
+      <c r="R24" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1498</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1499</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1500</v>
+      </c>
+      <c r="J25" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K25" t="s">
+        <v>1502</v>
+      </c>
+      <c r="L25" t="s">
+        <v>1503</v>
+      </c>
+      <c r="M25">
+        <v>77</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>2</v>
+      </c>
+      <c r="P25">
+        <v>3</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1510</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1511</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J26" t="s">
+        <v>1513</v>
+      </c>
+      <c r="K26" t="s">
+        <v>1514</v>
+      </c>
+      <c r="L26" t="s">
+        <v>1515</v>
+      </c>
+      <c r="M26">
+        <v>89</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1520</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1522</v>
+      </c>
+      <c r="I27" t="s">
+        <v>1523</v>
+      </c>
+      <c r="J27" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K27" t="s">
+        <v>1525</v>
+      </c>
+      <c r="L27" t="s">
+        <v>1526</v>
+      </c>
+      <c r="M27">
+        <v>23</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>2</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>13</v>
+      </c>
+      <c r="R27" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1531</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1532</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1533</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1534</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1535</v>
+      </c>
+      <c r="J28" t="s">
+        <v>1536</v>
+      </c>
+      <c r="K28" t="s">
+        <v>1537</v>
+      </c>
+      <c r="L28" t="s">
+        <v>1538</v>
+      </c>
+      <c r="M28">
+        <v>23</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>10</v>
+      </c>
+      <c r="R28" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1545</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1546</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1547</v>
+      </c>
+      <c r="J29" t="s">
+        <v>1548</v>
+      </c>
+      <c r="K29" t="s">
+        <v>1549</v>
+      </c>
+      <c r="L29" t="s">
+        <v>1550</v>
+      </c>
+      <c r="M29">
+        <v>79</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>8</v>
+      </c>
+      <c r="R29" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1557</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1558</v>
+      </c>
+      <c r="I30" t="s">
+        <v>1559</v>
+      </c>
+      <c r="J30" t="s">
+        <v>1560</v>
+      </c>
+      <c r="K30" t="s">
+        <v>1561</v>
+      </c>
+      <c r="L30" t="s">
+        <v>1562</v>
+      </c>
+      <c r="M30">
+        <v>79</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>2</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>6</v>
+      </c>
+      <c r="R30" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1569</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1571</v>
+      </c>
+      <c r="J31" t="s">
+        <v>1572</v>
+      </c>
+      <c r="K31" t="s">
+        <v>1573</v>
+      </c>
+      <c r="L31" t="s">
+        <v>1574</v>
+      </c>
+      <c r="M31">
+        <v>77</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>2</v>
+      </c>
+      <c r="P31">
+        <v>3</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1580</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1582</v>
+      </c>
+      <c r="I32" t="s">
+        <v>1583</v>
+      </c>
+      <c r="J32" t="s">
+        <v>1584</v>
+      </c>
+      <c r="K32" t="s">
+        <v>1585</v>
+      </c>
+      <c r="L32" t="s">
+        <v>1586</v>
+      </c>
+      <c r="M32">
+        <v>89</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1592</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1593</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1594</v>
+      </c>
+      <c r="J33" t="s">
+        <v>1595</v>
+      </c>
+      <c r="K33" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L33" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M33">
+        <v>23</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>2</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>13</v>
+      </c>
+      <c r="R33" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1602</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1603</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1604</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1605</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1606</v>
+      </c>
+      <c r="J34" t="s">
+        <v>1607</v>
+      </c>
+      <c r="K34" t="s">
+        <v>1608</v>
+      </c>
+      <c r="L34" t="s">
+        <v>1609</v>
+      </c>
+      <c r="M34">
+        <v>23</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>2</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>10</v>
+      </c>
+      <c r="R34" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1616</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1617</v>
+      </c>
+      <c r="I35" t="s">
+        <v>1618</v>
+      </c>
+      <c r="J35" t="s">
+        <v>1619</v>
+      </c>
+      <c r="K35" t="s">
+        <v>1620</v>
+      </c>
+      <c r="L35" t="s">
+        <v>1621</v>
+      </c>
+      <c r="M35">
+        <v>79</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>2</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>8</v>
+      </c>
+      <c r="R35" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1627</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1628</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1629</v>
+      </c>
+      <c r="I36" t="s">
+        <v>1630</v>
+      </c>
+      <c r="J36" t="s">
+        <v>1631</v>
+      </c>
+      <c r="K36" t="s">
+        <v>1632</v>
+      </c>
+      <c r="L36" t="s">
+        <v>1633</v>
+      </c>
+      <c r="M36">
+        <v>79</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>6</v>
+      </c>
+      <c r="R36" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1637</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1638</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1639</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1640</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1641</v>
+      </c>
+      <c r="I37" t="s">
+        <v>1642</v>
+      </c>
+      <c r="J37" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K37" t="s">
+        <v>1644</v>
+      </c>
+      <c r="L37" t="s">
+        <v>1645</v>
+      </c>
+      <c r="M37">
+        <v>77</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>2</v>
+      </c>
+      <c r="P37">
+        <v>3</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1649</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1653</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1654</v>
+      </c>
+      <c r="J38" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K38" t="s">
+        <v>1656</v>
+      </c>
+      <c r="L38" t="s">
+        <v>1657</v>
+      </c>
+      <c r="M38">
+        <v>89</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1662</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1663</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1664</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1665</v>
+      </c>
+      <c r="J39" t="s">
+        <v>1666</v>
+      </c>
+      <c r="K39" t="s">
+        <v>1667</v>
+      </c>
+      <c r="L39" t="s">
+        <v>1668</v>
+      </c>
+      <c r="M39">
+        <v>23</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>2</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>13</v>
+      </c>
+      <c r="R39" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1676</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1677</v>
+      </c>
+      <c r="J40" t="s">
+        <v>1678</v>
+      </c>
+      <c r="K40" t="s">
+        <v>1679</v>
+      </c>
+      <c r="L40" t="s">
+        <v>1680</v>
+      </c>
+      <c r="M40">
+        <v>23</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>2</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>10</v>
+      </c>
+      <c r="R40" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1684</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1686</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1687</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1688</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1689</v>
+      </c>
+      <c r="J41" t="s">
+        <v>1690</v>
+      </c>
+      <c r="K41" t="s">
+        <v>1691</v>
+      </c>
+      <c r="L41" t="s">
+        <v>1692</v>
+      </c>
+      <c r="M41">
+        <v>79</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>2</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>8</v>
+      </c>
+      <c r="R41" t="s">
+        <v>1693</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/output_to.xlsx
+++ b/output_to.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="1694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="2893">
   <si>
     <t>SL.No</t>
     <phoneticPr fontId="1"/>
@@ -6789,6 +6789,4802 @@
   </si>
   <si>
     <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SL.No</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Flt No.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep FltNo.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Regn No.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Origin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dest</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr StdTyp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep Time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep StdTyp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MTOW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Landing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Normal HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Double HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Remote HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Parking</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 752E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIMQ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VAPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOCI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:26:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>51 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>51 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9,411.75</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 684</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 6872C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTICV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOBL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEBD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:29:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55R A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:30:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55R A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11,294.10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 187Y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 351</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTILZ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VAPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:34:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,823.52</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 6528J</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 6872C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTICO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VECC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEBD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>18:58:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>28 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:22:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>28 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10,352.92</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SL.No</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Flt No.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep FltNo.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Regn No.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Origin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dest</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr Time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arr StdTyp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep Time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dep StdTyp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MTOW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Landing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Normal HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Double HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Remote HRS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Parking</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 1422</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 421</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTISX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMSJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VERC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>67 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,683.40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 752E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIMQ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VAPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOCI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:26:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>51 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>51 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9,411.75</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 684</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 6872C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTICV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOBL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEBD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:29:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55R A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:30:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55R A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11,294.10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 187Y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 351</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTILZ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VAPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:32:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:34:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,823.52</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 341</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 928</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VASU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:43:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55L A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6,514.20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5056</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5057</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTNHX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:44:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIXY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOTP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:27:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,648.37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7141</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 7523</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIRF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOMY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:36:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,918.70</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 5936</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 972</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTIPO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEPU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEGT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,354.25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 6528J</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6E 6872C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTICO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VECC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VEBD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>18:58:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>28 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:22:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>28 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10,352.92</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2560</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 3103</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTQA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VIDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:04:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>76 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>80 R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36,913.80</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2869</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI 2872</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTTNV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VABB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:54:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:47:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44 A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8,685.60</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7073,63 +11869,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" t="s" s="1">
-        <v>1225</v>
+        <v>2281</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>1226</v>
+        <v>2282</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>1227</v>
+        <v>2283</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>1228</v>
+        <v>2284</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>1229</v>
+        <v>2285</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>1230</v>
+        <v>2286</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>1231</v>
+        <v>2287</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>1232</v>
+        <v>2288</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>1233</v>
+        <v>2289</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>1234</v>
+        <v>2290</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>1235</v>
+        <v>2291</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>1236</v>
+        <v>2292</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>1237</v>
+        <v>2293</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>1238</v>
+        <v>2294</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>1239</v>
+        <v>2295</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>1240</v>
+        <v>2296</v>
       </c>
       <c r="Q1" t="s" s="3">
-        <v>1241</v>
+        <v>2297</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>1242</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -7137,37 +11933,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1243</v>
+        <v>2299</v>
       </c>
       <c r="C2" t="s">
-        <v>1244</v>
+        <v>2300</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>1245</v>
+        <v>2301</v>
       </c>
       <c r="E2" t="s">
-        <v>1246</v>
+        <v>2302</v>
       </c>
       <c r="F2" t="s">
-        <v>1247</v>
+        <v>2303</v>
       </c>
       <c r="G2" t="s" s="3">
-        <v>1248</v>
+        <v>2304</v>
       </c>
       <c r="H2" t="s">
-        <v>1249</v>
+        <v>2305</v>
       </c>
       <c r="I2" t="s">
-        <v>1250</v>
+        <v>2306</v>
       </c>
       <c r="J2" t="s" s="3">
-        <v>1251</v>
+        <v>2307</v>
       </c>
       <c r="K2" t="s">
-        <v>1252</v>
+        <v>2308</v>
       </c>
       <c r="L2" t="s">
-        <v>1253</v>
+        <v>2309</v>
       </c>
       <c r="M2" s="3">
         <v>79</v>
@@ -7185,7 +11981,7 @@
         <v>6</v>
       </c>
       <c r="R2" t="s">
-        <v>1254</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -7193,37 +11989,37 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>1255</v>
+        <v>2311</v>
       </c>
       <c r="C3" t="s">
-        <v>1256</v>
+        <v>2312</v>
       </c>
       <c r="D3" t="s" s="3">
-        <v>1257</v>
+        <v>2313</v>
       </c>
       <c r="E3" t="s">
-        <v>1258</v>
+        <v>2314</v>
       </c>
       <c r="F3" t="s">
-        <v>1259</v>
+        <v>2315</v>
       </c>
       <c r="G3" t="s" s="3">
-        <v>1260</v>
+        <v>2316</v>
       </c>
       <c r="H3" t="s">
-        <v>1261</v>
+        <v>2317</v>
       </c>
       <c r="I3" t="s">
-        <v>1262</v>
+        <v>2318</v>
       </c>
       <c r="J3" t="s" s="3">
-        <v>1263</v>
+        <v>2319</v>
       </c>
       <c r="K3" t="s">
-        <v>1264</v>
+        <v>2320</v>
       </c>
       <c r="L3" t="s">
-        <v>1265</v>
+        <v>2321</v>
       </c>
       <c r="M3" s="3">
         <v>77</v>
@@ -7241,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>1266</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7249,37 +12045,37 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>1267</v>
+        <v>2323</v>
       </c>
       <c r="C4" t="s">
-        <v>1268</v>
+        <v>2324</v>
       </c>
       <c r="D4" t="s" s="3">
-        <v>1269</v>
+        <v>2325</v>
       </c>
       <c r="E4" t="s">
-        <v>1270</v>
+        <v>2326</v>
       </c>
       <c r="F4" t="s">
-        <v>1271</v>
+        <v>2327</v>
       </c>
       <c r="G4" t="s" s="3">
-        <v>1272</v>
+        <v>2328</v>
       </c>
       <c r="H4" t="s">
-        <v>1273</v>
+        <v>2329</v>
       </c>
       <c r="I4" t="s">
-        <v>1274</v>
+        <v>2330</v>
       </c>
       <c r="J4" t="s" s="3">
-        <v>1275</v>
+        <v>2331</v>
       </c>
       <c r="K4" t="s">
-        <v>1276</v>
+        <v>2332</v>
       </c>
       <c r="L4" t="s">
-        <v>1277</v>
+        <v>2333</v>
       </c>
       <c r="M4" s="3">
         <v>89</v>
@@ -7305,37 +12101,37 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>1278</v>
+        <v>2334</v>
       </c>
       <c r="C5" t="s">
-        <v>1279</v>
+        <v>2335</v>
       </c>
       <c r="D5" t="s" s="3">
-        <v>1280</v>
+        <v>2336</v>
       </c>
       <c r="E5" t="s">
-        <v>1281</v>
+        <v>2337</v>
       </c>
       <c r="F5" t="s">
-        <v>1282</v>
+        <v>2338</v>
       </c>
       <c r="G5" t="s" s="3">
-        <v>1283</v>
+        <v>2339</v>
       </c>
       <c r="H5" t="s">
-        <v>1284</v>
+        <v>2340</v>
       </c>
       <c r="I5" t="s">
-        <v>1285</v>
+        <v>2341</v>
       </c>
       <c r="J5" t="s" s="3">
-        <v>1286</v>
+        <v>2342</v>
       </c>
       <c r="K5" t="s">
-        <v>1287</v>
+        <v>2343</v>
       </c>
       <c r="L5" t="s">
-        <v>1288</v>
+        <v>2344</v>
       </c>
       <c r="M5" s="3">
         <v>23</v>
@@ -7353,7 +12149,7 @@
         <v>13</v>
       </c>
       <c r="R5" t="s">
-        <v>1289</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -7361,37 +12157,37 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>1290</v>
+        <v>2346</v>
       </c>
       <c r="C6" t="s">
-        <v>1291</v>
+        <v>2347</v>
       </c>
       <c r="D6" t="s">
-        <v>1292</v>
+        <v>2348</v>
       </c>
       <c r="E6" t="s">
-        <v>1293</v>
+        <v>2349</v>
       </c>
       <c r="F6" t="s">
-        <v>1294</v>
+        <v>2350</v>
       </c>
       <c r="G6" t="s">
-        <v>1295</v>
+        <v>2351</v>
       </c>
       <c r="H6" t="s">
-        <v>1296</v>
+        <v>2352</v>
       </c>
       <c r="I6" t="s">
-        <v>1297</v>
+        <v>2353</v>
       </c>
       <c r="J6" t="s">
-        <v>1298</v>
+        <v>2354</v>
       </c>
       <c r="K6" t="s">
-        <v>1299</v>
+        <v>2355</v>
       </c>
       <c r="L6" t="s">
-        <v>1300</v>
+        <v>2356</v>
       </c>
       <c r="M6">
         <v>23</v>
@@ -7409,7 +12205,7 @@
         <v>10</v>
       </c>
       <c r="R6" t="s">
-        <v>1301</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -7417,37 +12213,37 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>1302</v>
+        <v>2358</v>
       </c>
       <c r="C7" t="s">
-        <v>1303</v>
+        <v>2359</v>
       </c>
       <c r="D7" t="s">
-        <v>1304</v>
+        <v>2360</v>
       </c>
       <c r="E7" t="s">
-        <v>1305</v>
+        <v>2361</v>
       </c>
       <c r="F7" t="s">
-        <v>1306</v>
+        <v>2362</v>
       </c>
       <c r="G7" t="s">
-        <v>1307</v>
+        <v>2363</v>
       </c>
       <c r="H7" t="s">
-        <v>1308</v>
+        <v>2364</v>
       </c>
       <c r="I7" t="s">
-        <v>1309</v>
+        <v>2365</v>
       </c>
       <c r="J7" t="s">
-        <v>1310</v>
+        <v>2366</v>
       </c>
       <c r="K7" t="s">
-        <v>1311</v>
+        <v>2367</v>
       </c>
       <c r="L7" t="s">
-        <v>1312</v>
+        <v>2368</v>
       </c>
       <c r="M7">
         <v>79</v>
@@ -7465,7 +12261,7 @@
         <v>8</v>
       </c>
       <c r="R7" t="s">
-        <v>1313</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -7473,37 +12269,37 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>1314</v>
+        <v>2370</v>
       </c>
       <c r="C8" t="s">
-        <v>1315</v>
+        <v>2371</v>
       </c>
       <c r="D8" t="s">
-        <v>1316</v>
+        <v>2372</v>
       </c>
       <c r="E8" t="s">
-        <v>1317</v>
+        <v>2373</v>
       </c>
       <c r="F8" t="s">
-        <v>1318</v>
+        <v>2374</v>
       </c>
       <c r="G8" t="s">
-        <v>1319</v>
+        <v>2375</v>
       </c>
       <c r="H8" t="s">
-        <v>1320</v>
+        <v>2376</v>
       </c>
       <c r="I8" t="s">
-        <v>1321</v>
+        <v>2377</v>
       </c>
       <c r="J8" t="s">
-        <v>1322</v>
+        <v>2378</v>
       </c>
       <c r="K8" t="s">
-        <v>1323</v>
+        <v>2379</v>
       </c>
       <c r="L8" t="s">
-        <v>1324</v>
+        <v>2380</v>
       </c>
       <c r="M8">
         <v>77</v>
@@ -7521,7 +12317,7 @@
         <v>32</v>
       </c>
       <c r="R8" t="s">
-        <v>1325</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -7529,37 +12325,37 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>1326</v>
+        <v>2382</v>
       </c>
       <c r="C9" t="s">
-        <v>1327</v>
+        <v>2383</v>
       </c>
       <c r="D9" t="s">
-        <v>1328</v>
+        <v>2384</v>
       </c>
       <c r="E9" t="s">
-        <v>1329</v>
+        <v>2385</v>
       </c>
       <c r="F9" t="s">
-        <v>1330</v>
+        <v>2386</v>
       </c>
       <c r="G9" t="s">
-        <v>1331</v>
+        <v>2387</v>
       </c>
       <c r="H9" t="s">
-        <v>1332</v>
+        <v>2388</v>
       </c>
       <c r="I9" t="s">
-        <v>1333</v>
+        <v>2389</v>
       </c>
       <c r="J9" t="s">
-        <v>1334</v>
+        <v>2390</v>
       </c>
       <c r="K9" t="s">
-        <v>1335</v>
+        <v>2391</v>
       </c>
       <c r="L9" t="s">
-        <v>1336</v>
+        <v>2392</v>
       </c>
       <c r="M9">
         <v>77</v>
@@ -7577,7 +12373,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>1337</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -7585,37 +12381,37 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>1338</v>
+        <v>2394</v>
       </c>
       <c r="C10" t="s">
-        <v>1339</v>
+        <v>2395</v>
       </c>
       <c r="D10" t="s">
-        <v>1340</v>
+        <v>2396</v>
       </c>
       <c r="E10" t="s">
-        <v>1341</v>
+        <v>2397</v>
       </c>
       <c r="F10" t="s">
-        <v>1342</v>
+        <v>2398</v>
       </c>
       <c r="G10" t="s">
-        <v>1343</v>
+        <v>2399</v>
       </c>
       <c r="H10" t="s">
-        <v>1344</v>
+        <v>2400</v>
       </c>
       <c r="I10" t="s">
-        <v>1345</v>
+        <v>2401</v>
       </c>
       <c r="J10" t="s">
-        <v>1346</v>
+        <v>2402</v>
       </c>
       <c r="K10" t="s">
-        <v>1347</v>
+        <v>2403</v>
       </c>
       <c r="L10" t="s">
-        <v>1348</v>
+        <v>2404</v>
       </c>
       <c r="M10">
         <v>77</v>
@@ -7633,7 +12429,7 @@
         <v>32</v>
       </c>
       <c r="R10" t="s">
-        <v>1349</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -7641,37 +12437,37 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>1350</v>
+        <v>2406</v>
       </c>
       <c r="C11" t="s">
-        <v>1351</v>
+        <v>2407</v>
       </c>
       <c r="D11" t="s">
-        <v>1352</v>
+        <v>2408</v>
       </c>
       <c r="E11" t="s">
-        <v>1353</v>
+        <v>2409</v>
       </c>
       <c r="F11" t="s">
-        <v>1354</v>
+        <v>2410</v>
       </c>
       <c r="G11" t="s">
-        <v>1355</v>
+        <v>2411</v>
       </c>
       <c r="H11" t="s">
-        <v>1356</v>
+        <v>2412</v>
       </c>
       <c r="I11" t="s">
-        <v>1357</v>
+        <v>2413</v>
       </c>
       <c r="J11" t="s">
-        <v>1358</v>
+        <v>2414</v>
       </c>
       <c r="K11" t="s">
-        <v>1359</v>
+        <v>2415</v>
       </c>
       <c r="L11" t="s">
-        <v>1360</v>
+        <v>2416</v>
       </c>
       <c r="M11">
         <v>77</v>
@@ -7689,7 +12485,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>1361</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -7697,37 +12493,37 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>1362</v>
+        <v>2418</v>
       </c>
       <c r="C12" t="s">
-        <v>1363</v>
+        <v>2419</v>
       </c>
       <c r="D12" t="s">
-        <v>1364</v>
+        <v>2420</v>
       </c>
       <c r="E12" t="s">
-        <v>1365</v>
+        <v>2421</v>
       </c>
       <c r="F12" t="s">
-        <v>1366</v>
+        <v>2422</v>
       </c>
       <c r="G12" t="s">
-        <v>1367</v>
+        <v>2423</v>
       </c>
       <c r="H12" t="s">
-        <v>1368</v>
+        <v>2424</v>
       </c>
       <c r="I12" t="s">
-        <v>1369</v>
+        <v>2425</v>
       </c>
       <c r="J12" t="s">
-        <v>1370</v>
+        <v>2426</v>
       </c>
       <c r="K12" t="s">
-        <v>1371</v>
+        <v>2427</v>
       </c>
       <c r="L12" t="s">
-        <v>1372</v>
+        <v>2428</v>
       </c>
       <c r="M12">
         <v>77</v>
@@ -7745,7 +12541,7 @@
         <v>32</v>
       </c>
       <c r="R12" t="s">
-        <v>1373</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -7753,37 +12549,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>1374</v>
+        <v>2430</v>
       </c>
       <c r="C13" t="s">
-        <v>1375</v>
+        <v>2431</v>
       </c>
       <c r="D13" t="s">
-        <v>1376</v>
+        <v>2432</v>
       </c>
       <c r="E13" t="s">
-        <v>1377</v>
+        <v>2433</v>
       </c>
       <c r="F13" t="s">
-        <v>1378</v>
+        <v>2434</v>
       </c>
       <c r="G13" t="s">
-        <v>1379</v>
+        <v>2435</v>
       </c>
       <c r="H13" t="s">
-        <v>1380</v>
+        <v>2436</v>
       </c>
       <c r="I13" t="s">
-        <v>1381</v>
+        <v>2437</v>
       </c>
       <c r="J13" t="s">
-        <v>1382</v>
+        <v>2438</v>
       </c>
       <c r="K13" t="s">
-        <v>1383</v>
+        <v>2439</v>
       </c>
       <c r="L13" t="s">
-        <v>1384</v>
+        <v>2440</v>
       </c>
       <c r="M13">
         <v>77</v>
@@ -7801,7 +12597,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>1385</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -7809,37 +12605,37 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>1386</v>
+        <v>2442</v>
       </c>
       <c r="C14" t="s">
-        <v>1387</v>
+        <v>2443</v>
       </c>
       <c r="D14" t="s">
-        <v>1388</v>
+        <v>2444</v>
       </c>
       <c r="E14" t="s">
-        <v>1389</v>
+        <v>2445</v>
       </c>
       <c r="F14" t="s">
-        <v>1390</v>
+        <v>2446</v>
       </c>
       <c r="G14" t="s">
-        <v>1391</v>
+        <v>2447</v>
       </c>
       <c r="H14" t="s">
-        <v>1392</v>
+        <v>2448</v>
       </c>
       <c r="I14" t="s">
-        <v>1393</v>
+        <v>2449</v>
       </c>
       <c r="J14" t="s">
-        <v>1394</v>
+        <v>2450</v>
       </c>
       <c r="K14" t="s">
-        <v>1395</v>
+        <v>2451</v>
       </c>
       <c r="L14" t="s">
-        <v>1396</v>
+        <v>2452</v>
       </c>
       <c r="M14">
         <v>79</v>
@@ -7857,7 +12653,7 @@
         <v>6</v>
       </c>
       <c r="R14" t="s">
-        <v>1397</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -7865,37 +12661,37 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>1398</v>
+        <v>2454</v>
       </c>
       <c r="C15" t="s">
-        <v>1399</v>
+        <v>2455</v>
       </c>
       <c r="D15" t="s">
-        <v>1400</v>
+        <v>2456</v>
       </c>
       <c r="E15" t="s">
-        <v>1401</v>
+        <v>2457</v>
       </c>
       <c r="F15" t="s">
-        <v>1402</v>
+        <v>2458</v>
       </c>
       <c r="G15" t="s">
-        <v>1403</v>
+        <v>2459</v>
       </c>
       <c r="H15" t="s">
-        <v>1404</v>
+        <v>2460</v>
       </c>
       <c r="I15" t="s">
-        <v>1405</v>
+        <v>2461</v>
       </c>
       <c r="J15" t="s">
-        <v>1406</v>
+        <v>2462</v>
       </c>
       <c r="K15" t="s">
-        <v>1407</v>
+        <v>2463</v>
       </c>
       <c r="L15" t="s">
-        <v>1408</v>
+        <v>2464</v>
       </c>
       <c r="M15">
         <v>77</v>
@@ -7913,7 +12709,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>1409</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -7921,37 +12717,37 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>1410</v>
+        <v>2466</v>
       </c>
       <c r="C16" t="s">
-        <v>1411</v>
+        <v>2467</v>
       </c>
       <c r="D16" t="s">
-        <v>1412</v>
+        <v>2468</v>
       </c>
       <c r="E16" t="s">
-        <v>1413</v>
+        <v>2469</v>
       </c>
       <c r="F16" t="s">
-        <v>1414</v>
+        <v>2470</v>
       </c>
       <c r="G16" t="s">
-        <v>1415</v>
+        <v>2471</v>
       </c>
       <c r="H16" t="s">
-        <v>1416</v>
+        <v>2472</v>
       </c>
       <c r="I16" t="s">
-        <v>1417</v>
+        <v>2473</v>
       </c>
       <c r="J16" t="s">
-        <v>1418</v>
+        <v>2474</v>
       </c>
       <c r="K16" t="s">
-        <v>1419</v>
+        <v>2475</v>
       </c>
       <c r="L16" t="s">
-        <v>1420</v>
+        <v>2476</v>
       </c>
       <c r="M16">
         <v>89</v>
@@ -7977,37 +12773,37 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>1421</v>
+        <v>2477</v>
       </c>
       <c r="C17" t="s">
-        <v>1422</v>
+        <v>2478</v>
       </c>
       <c r="D17" t="s">
-        <v>1423</v>
+        <v>2479</v>
       </c>
       <c r="E17" t="s">
-        <v>1424</v>
+        <v>2480</v>
       </c>
       <c r="F17" t="s">
-        <v>1425</v>
+        <v>2481</v>
       </c>
       <c r="G17" t="s">
-        <v>1426</v>
+        <v>2482</v>
       </c>
       <c r="H17" t="s">
-        <v>1427</v>
+        <v>2483</v>
       </c>
       <c r="I17" t="s">
-        <v>1428</v>
+        <v>2484</v>
       </c>
       <c r="J17" t="s">
-        <v>1429</v>
+        <v>2485</v>
       </c>
       <c r="K17" t="s">
-        <v>1430</v>
+        <v>2486</v>
       </c>
       <c r="L17" t="s">
-        <v>1431</v>
+        <v>2487</v>
       </c>
       <c r="M17">
         <v>23</v>
@@ -8025,7 +12821,7 @@
         <v>13</v>
       </c>
       <c r="R17" t="s">
-        <v>1432</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -8033,37 +12829,37 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>1433</v>
+        <v>2489</v>
       </c>
       <c r="C18" t="s">
-        <v>1434</v>
+        <v>2490</v>
       </c>
       <c r="D18" t="s">
-        <v>1435</v>
+        <v>2491</v>
       </c>
       <c r="E18" t="s">
-        <v>1436</v>
+        <v>2492</v>
       </c>
       <c r="F18" t="s">
-        <v>1437</v>
+        <v>2493</v>
       </c>
       <c r="G18" t="s">
-        <v>1438</v>
+        <v>2494</v>
       </c>
       <c r="H18" t="s">
-        <v>1439</v>
+        <v>2495</v>
       </c>
       <c r="I18" t="s">
-        <v>1440</v>
+        <v>2496</v>
       </c>
       <c r="J18" t="s">
-        <v>1441</v>
+        <v>2497</v>
       </c>
       <c r="K18" t="s">
-        <v>1442</v>
+        <v>2498</v>
       </c>
       <c r="L18" t="s">
-        <v>1443</v>
+        <v>2499</v>
       </c>
       <c r="M18">
         <v>23</v>
@@ -8081,7 +12877,7 @@
         <v>10</v>
       </c>
       <c r="R18" t="s">
-        <v>1444</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -8089,37 +12885,37 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>1445</v>
+        <v>2501</v>
       </c>
       <c r="C19" t="s">
-        <v>1446</v>
+        <v>2502</v>
       </c>
       <c r="D19" t="s">
-        <v>1447</v>
+        <v>2503</v>
       </c>
       <c r="E19" t="s">
-        <v>1448</v>
+        <v>2504</v>
       </c>
       <c r="F19" t="s">
-        <v>1449</v>
+        <v>2505</v>
       </c>
       <c r="G19" t="s">
-        <v>1450</v>
+        <v>2506</v>
       </c>
       <c r="H19" t="s">
-        <v>1451</v>
+        <v>2507</v>
       </c>
       <c r="I19" t="s">
-        <v>1452</v>
+        <v>2508</v>
       </c>
       <c r="J19" t="s">
-        <v>1453</v>
+        <v>2509</v>
       </c>
       <c r="K19" t="s">
-        <v>1454</v>
+        <v>2510</v>
       </c>
       <c r="L19" t="s">
-        <v>1455</v>
+        <v>2511</v>
       </c>
       <c r="M19">
         <v>79</v>
@@ -8137,7 +12933,7 @@
         <v>8</v>
       </c>
       <c r="R19" t="s">
-        <v>1456</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="21" spans="6:6">
@@ -8148,37 +12944,37 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>1457</v>
+        <v>2513</v>
       </c>
       <c r="C22" t="s">
-        <v>1458</v>
+        <v>2514</v>
       </c>
       <c r="D22" t="s">
-        <v>1459</v>
+        <v>2515</v>
       </c>
       <c r="E22" t="s">
-        <v>1460</v>
+        <v>2516</v>
       </c>
       <c r="F22" t="s">
-        <v>1461</v>
+        <v>2517</v>
       </c>
       <c r="G22" t="s">
-        <v>1462</v>
+        <v>2518</v>
       </c>
       <c r="H22" t="s">
-        <v>1463</v>
+        <v>2519</v>
       </c>
       <c r="I22" t="s">
-        <v>1464</v>
+        <v>2520</v>
       </c>
       <c r="J22" t="s">
-        <v>1465</v>
+        <v>2521</v>
       </c>
       <c r="K22" t="s">
-        <v>1466</v>
+        <v>2522</v>
       </c>
       <c r="L22" t="s">
-        <v>1467</v>
+        <v>2523</v>
       </c>
       <c r="M22">
         <v>77</v>
@@ -8196,7 +12992,7 @@
         <v>32</v>
       </c>
       <c r="R22" t="s">
-        <v>1468</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -8204,37 +13000,37 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>1469</v>
+        <v>2525</v>
       </c>
       <c r="C23" t="s">
-        <v>1470</v>
+        <v>2526</v>
       </c>
       <c r="D23" t="s">
-        <v>1471</v>
+        <v>2527</v>
       </c>
       <c r="E23" t="s">
-        <v>1472</v>
+        <v>2528</v>
       </c>
       <c r="F23" t="s">
-        <v>1473</v>
+        <v>2529</v>
       </c>
       <c r="G23" t="s">
-        <v>1474</v>
+        <v>2530</v>
       </c>
       <c r="H23" t="s">
-        <v>1475</v>
+        <v>2531</v>
       </c>
       <c r="I23" t="s">
-        <v>1476</v>
+        <v>2532</v>
       </c>
       <c r="J23" t="s">
-        <v>1477</v>
+        <v>2533</v>
       </c>
       <c r="K23" t="s">
-        <v>1478</v>
+        <v>2534</v>
       </c>
       <c r="L23" t="s">
-        <v>1479</v>
+        <v>2535</v>
       </c>
       <c r="M23">
         <v>77</v>
@@ -8252,7 +13048,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>1480</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -8260,37 +13056,37 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>1481</v>
+        <v>2537</v>
       </c>
       <c r="C24" t="s">
-        <v>1482</v>
+        <v>2538</v>
       </c>
       <c r="D24" t="s">
-        <v>1483</v>
+        <v>2539</v>
       </c>
       <c r="E24" t="s">
-        <v>1484</v>
+        <v>2540</v>
       </c>
       <c r="F24" t="s">
-        <v>1485</v>
+        <v>2541</v>
       </c>
       <c r="G24" t="s">
-        <v>1486</v>
+        <v>2542</v>
       </c>
       <c r="H24" t="s">
-        <v>1487</v>
+        <v>2543</v>
       </c>
       <c r="I24" t="s">
-        <v>1488</v>
+        <v>2544</v>
       </c>
       <c r="J24" t="s">
-        <v>1489</v>
+        <v>2545</v>
       </c>
       <c r="K24" t="s">
-        <v>1490</v>
+        <v>2546</v>
       </c>
       <c r="L24" t="s">
-        <v>1491</v>
+        <v>2547</v>
       </c>
       <c r="M24">
         <v>79</v>
@@ -8308,7 +13104,7 @@
         <v>6</v>
       </c>
       <c r="R24" t="s">
-        <v>1492</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -8316,37 +13112,37 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>1493</v>
+        <v>2549</v>
       </c>
       <c r="C25" t="s">
-        <v>1494</v>
+        <v>2550</v>
       </c>
       <c r="D25" t="s">
-        <v>1495</v>
+        <v>2551</v>
       </c>
       <c r="E25" t="s">
-        <v>1496</v>
+        <v>2552</v>
       </c>
       <c r="F25" t="s">
-        <v>1497</v>
+        <v>2553</v>
       </c>
       <c r="G25" t="s">
-        <v>1498</v>
+        <v>2554</v>
       </c>
       <c r="H25" t="s">
-        <v>1499</v>
+        <v>2555</v>
       </c>
       <c r="I25" t="s">
-        <v>1500</v>
+        <v>2556</v>
       </c>
       <c r="J25" t="s">
-        <v>1501</v>
+        <v>2557</v>
       </c>
       <c r="K25" t="s">
-        <v>1502</v>
+        <v>2558</v>
       </c>
       <c r="L25" t="s">
-        <v>1503</v>
+        <v>2559</v>
       </c>
       <c r="M25">
         <v>77</v>
@@ -8364,7 +13160,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>1504</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -8372,37 +13168,37 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>1505</v>
+        <v>2561</v>
       </c>
       <c r="C26" t="s">
-        <v>1506</v>
+        <v>2562</v>
       </c>
       <c r="D26" t="s">
-        <v>1507</v>
+        <v>2563</v>
       </c>
       <c r="E26" t="s">
-        <v>1508</v>
+        <v>2564</v>
       </c>
       <c r="F26" t="s">
-        <v>1509</v>
+        <v>2565</v>
       </c>
       <c r="G26" t="s">
-        <v>1510</v>
+        <v>2566</v>
       </c>
       <c r="H26" t="s">
-        <v>1511</v>
+        <v>2567</v>
       </c>
       <c r="I26" t="s">
-        <v>1512</v>
+        <v>2568</v>
       </c>
       <c r="J26" t="s">
-        <v>1513</v>
+        <v>2569</v>
       </c>
       <c r="K26" t="s">
-        <v>1514</v>
+        <v>2570</v>
       </c>
       <c r="L26" t="s">
-        <v>1515</v>
+        <v>2571</v>
       </c>
       <c r="M26">
         <v>89</v>
@@ -8428,37 +13224,37 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>1516</v>
+        <v>2572</v>
       </c>
       <c r="C27" t="s">
-        <v>1517</v>
+        <v>2573</v>
       </c>
       <c r="D27" t="s">
-        <v>1518</v>
+        <v>2574</v>
       </c>
       <c r="E27" t="s">
-        <v>1519</v>
+        <v>2575</v>
       </c>
       <c r="F27" t="s">
-        <v>1520</v>
+        <v>2576</v>
       </c>
       <c r="G27" t="s">
-        <v>1521</v>
+        <v>2577</v>
       </c>
       <c r="H27" t="s">
-        <v>1522</v>
+        <v>2578</v>
       </c>
       <c r="I27" t="s">
-        <v>1523</v>
+        <v>2579</v>
       </c>
       <c r="J27" t="s">
-        <v>1524</v>
+        <v>2580</v>
       </c>
       <c r="K27" t="s">
-        <v>1525</v>
+        <v>2581</v>
       </c>
       <c r="L27" t="s">
-        <v>1526</v>
+        <v>2582</v>
       </c>
       <c r="M27">
         <v>23</v>
@@ -8476,7 +13272,7 @@
         <v>13</v>
       </c>
       <c r="R27" t="s">
-        <v>1527</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -8484,37 +13280,37 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>1528</v>
+        <v>2584</v>
       </c>
       <c r="C28" t="s">
-        <v>1529</v>
+        <v>2585</v>
       </c>
       <c r="D28" t="s">
-        <v>1530</v>
+        <v>2586</v>
       </c>
       <c r="E28" t="s">
-        <v>1531</v>
+        <v>2587</v>
       </c>
       <c r="F28" t="s">
-        <v>1532</v>
+        <v>2588</v>
       </c>
       <c r="G28" t="s">
-        <v>1533</v>
+        <v>2589</v>
       </c>
       <c r="H28" t="s">
-        <v>1534</v>
+        <v>2590</v>
       </c>
       <c r="I28" t="s">
-        <v>1535</v>
+        <v>2591</v>
       </c>
       <c r="J28" t="s">
-        <v>1536</v>
+        <v>2592</v>
       </c>
       <c r="K28" t="s">
-        <v>1537</v>
+        <v>2593</v>
       </c>
       <c r="L28" t="s">
-        <v>1538</v>
+        <v>2594</v>
       </c>
       <c r="M28">
         <v>23</v>
@@ -8532,7 +13328,7 @@
         <v>10</v>
       </c>
       <c r="R28" t="s">
-        <v>1539</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -8540,37 +13336,37 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>1540</v>
+        <v>2596</v>
       </c>
       <c r="C29" t="s">
-        <v>1541</v>
+        <v>2597</v>
       </c>
       <c r="D29" t="s">
-        <v>1542</v>
+        <v>2598</v>
       </c>
       <c r="E29" t="s">
-        <v>1543</v>
+        <v>2599</v>
       </c>
       <c r="F29" t="s">
-        <v>1544</v>
+        <v>2600</v>
       </c>
       <c r="G29" t="s">
-        <v>1545</v>
+        <v>2601</v>
       </c>
       <c r="H29" t="s">
-        <v>1546</v>
+        <v>2602</v>
       </c>
       <c r="I29" t="s">
-        <v>1547</v>
+        <v>2603</v>
       </c>
       <c r="J29" t="s">
-        <v>1548</v>
+        <v>2604</v>
       </c>
       <c r="K29" t="s">
-        <v>1549</v>
+        <v>2605</v>
       </c>
       <c r="L29" t="s">
-        <v>1550</v>
+        <v>2606</v>
       </c>
       <c r="M29">
         <v>79</v>
@@ -8588,7 +13384,7 @@
         <v>8</v>
       </c>
       <c r="R29" t="s">
-        <v>1551</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -8596,37 +13392,37 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>1552</v>
+        <v>2608</v>
       </c>
       <c r="C30" t="s">
-        <v>1553</v>
+        <v>2609</v>
       </c>
       <c r="D30" t="s">
-        <v>1554</v>
+        <v>2610</v>
       </c>
       <c r="E30" t="s">
-        <v>1555</v>
+        <v>2611</v>
       </c>
       <c r="F30" t="s">
-        <v>1556</v>
+        <v>2612</v>
       </c>
       <c r="G30" t="s">
-        <v>1557</v>
+        <v>2613</v>
       </c>
       <c r="H30" t="s">
-        <v>1558</v>
+        <v>2614</v>
       </c>
       <c r="I30" t="s">
-        <v>1559</v>
+        <v>2615</v>
       </c>
       <c r="J30" t="s">
-        <v>1560</v>
+        <v>2616</v>
       </c>
       <c r="K30" t="s">
-        <v>1561</v>
+        <v>2617</v>
       </c>
       <c r="L30" t="s">
-        <v>1562</v>
+        <v>2618</v>
       </c>
       <c r="M30">
         <v>79</v>
@@ -8644,7 +13440,7 @@
         <v>6</v>
       </c>
       <c r="R30" t="s">
-        <v>1563</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -8652,37 +13448,37 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>1564</v>
+        <v>2620</v>
       </c>
       <c r="C31" t="s">
-        <v>1565</v>
+        <v>2621</v>
       </c>
       <c r="D31" t="s">
-        <v>1566</v>
+        <v>2622</v>
       </c>
       <c r="E31" t="s">
-        <v>1567</v>
+        <v>2623</v>
       </c>
       <c r="F31" t="s">
-        <v>1568</v>
+        <v>2624</v>
       </c>
       <c r="G31" t="s">
-        <v>1569</v>
+        <v>2625</v>
       </c>
       <c r="H31" t="s">
-        <v>1570</v>
+        <v>2626</v>
       </c>
       <c r="I31" t="s">
-        <v>1571</v>
+        <v>2627</v>
       </c>
       <c r="J31" t="s">
-        <v>1572</v>
+        <v>2628</v>
       </c>
       <c r="K31" t="s">
-        <v>1573</v>
+        <v>2629</v>
       </c>
       <c r="L31" t="s">
-        <v>1574</v>
+        <v>2630</v>
       </c>
       <c r="M31">
         <v>77</v>
@@ -8700,7 +13496,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>1575</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -8708,37 +13504,37 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>1576</v>
+        <v>2632</v>
       </c>
       <c r="C32" t="s">
-        <v>1577</v>
+        <v>2633</v>
       </c>
       <c r="D32" t="s">
-        <v>1578</v>
+        <v>2634</v>
       </c>
       <c r="E32" t="s">
-        <v>1579</v>
+        <v>2635</v>
       </c>
       <c r="F32" t="s">
-        <v>1580</v>
+        <v>2636</v>
       </c>
       <c r="G32" t="s">
-        <v>1581</v>
+        <v>2637</v>
       </c>
       <c r="H32" t="s">
-        <v>1582</v>
+        <v>2638</v>
       </c>
       <c r="I32" t="s">
-        <v>1583</v>
+        <v>2639</v>
       </c>
       <c r="J32" t="s">
-        <v>1584</v>
+        <v>2640</v>
       </c>
       <c r="K32" t="s">
-        <v>1585</v>
+        <v>2641</v>
       </c>
       <c r="L32" t="s">
-        <v>1586</v>
+        <v>2642</v>
       </c>
       <c r="M32">
         <v>89</v>
@@ -8764,37 +13560,37 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>1587</v>
+        <v>2643</v>
       </c>
       <c r="C33" t="s">
-        <v>1588</v>
+        <v>2644</v>
       </c>
       <c r="D33" t="s">
-        <v>1589</v>
+        <v>2645</v>
       </c>
       <c r="E33" t="s">
-        <v>1590</v>
+        <v>2646</v>
       </c>
       <c r="F33" t="s">
-        <v>1591</v>
+        <v>2647</v>
       </c>
       <c r="G33" t="s">
-        <v>1592</v>
+        <v>2648</v>
       </c>
       <c r="H33" t="s">
-        <v>1593</v>
+        <v>2649</v>
       </c>
       <c r="I33" t="s">
-        <v>1594</v>
+        <v>2650</v>
       </c>
       <c r="J33" t="s">
-        <v>1595</v>
+        <v>2651</v>
       </c>
       <c r="K33" t="s">
-        <v>1596</v>
+        <v>2652</v>
       </c>
       <c r="L33" t="s">
-        <v>1597</v>
+        <v>2653</v>
       </c>
       <c r="M33">
         <v>23</v>
@@ -8812,7 +13608,7 @@
         <v>13</v>
       </c>
       <c r="R33" t="s">
-        <v>1598</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -8820,37 +13616,37 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>1599</v>
+        <v>2655</v>
       </c>
       <c r="C34" t="s">
-        <v>1600</v>
+        <v>2656</v>
       </c>
       <c r="D34" t="s">
-        <v>1601</v>
+        <v>2657</v>
       </c>
       <c r="E34" t="s">
-        <v>1602</v>
+        <v>2658</v>
       </c>
       <c r="F34" t="s">
-        <v>1603</v>
+        <v>2659</v>
       </c>
       <c r="G34" t="s">
-        <v>1604</v>
+        <v>2660</v>
       </c>
       <c r="H34" t="s">
-        <v>1605</v>
+        <v>2661</v>
       </c>
       <c r="I34" t="s">
-        <v>1606</v>
+        <v>2662</v>
       </c>
       <c r="J34" t="s">
-        <v>1607</v>
+        <v>2663</v>
       </c>
       <c r="K34" t="s">
-        <v>1608</v>
+        <v>2664</v>
       </c>
       <c r="L34" t="s">
-        <v>1609</v>
+        <v>2665</v>
       </c>
       <c r="M34">
         <v>23</v>
@@ -8868,7 +13664,7 @@
         <v>10</v>
       </c>
       <c r="R34" t="s">
-        <v>1610</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -8876,37 +13672,37 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>1611</v>
+        <v>2667</v>
       </c>
       <c r="C35" t="s">
-        <v>1612</v>
+        <v>2668</v>
       </c>
       <c r="D35" t="s">
-        <v>1613</v>
+        <v>2669</v>
       </c>
       <c r="E35" t="s">
-        <v>1614</v>
+        <v>2670</v>
       </c>
       <c r="F35" t="s">
-        <v>1615</v>
+        <v>2671</v>
       </c>
       <c r="G35" t="s">
-        <v>1616</v>
+        <v>2672</v>
       </c>
       <c r="H35" t="s">
-        <v>1617</v>
+        <v>2673</v>
       </c>
       <c r="I35" t="s">
-        <v>1618</v>
+        <v>2674</v>
       </c>
       <c r="J35" t="s">
-        <v>1619</v>
+        <v>2675</v>
       </c>
       <c r="K35" t="s">
-        <v>1620</v>
+        <v>2676</v>
       </c>
       <c r="L35" t="s">
-        <v>1621</v>
+        <v>2677</v>
       </c>
       <c r="M35">
         <v>79</v>
@@ -8924,7 +13720,7 @@
         <v>8</v>
       </c>
       <c r="R35" t="s">
-        <v>1622</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -8932,37 +13728,37 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>1623</v>
+        <v>2679</v>
       </c>
       <c r="C36" t="s">
-        <v>1624</v>
+        <v>2680</v>
       </c>
       <c r="D36" t="s">
-        <v>1625</v>
+        <v>2681</v>
       </c>
       <c r="E36" t="s">
-        <v>1626</v>
+        <v>2682</v>
       </c>
       <c r="F36" t="s">
-        <v>1627</v>
+        <v>2683</v>
       </c>
       <c r="G36" t="s">
-        <v>1628</v>
+        <v>2684</v>
       </c>
       <c r="H36" t="s">
-        <v>1629</v>
+        <v>2685</v>
       </c>
       <c r="I36" t="s">
-        <v>1630</v>
+        <v>2686</v>
       </c>
       <c r="J36" t="s">
-        <v>1631</v>
+        <v>2687</v>
       </c>
       <c r="K36" t="s">
-        <v>1632</v>
+        <v>2688</v>
       </c>
       <c r="L36" t="s">
-        <v>1633</v>
+        <v>2689</v>
       </c>
       <c r="M36">
         <v>79</v>
@@ -8980,7 +13776,7 @@
         <v>6</v>
       </c>
       <c r="R36" t="s">
-        <v>1634</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -8988,37 +13784,37 @@
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>1635</v>
+        <v>2691</v>
       </c>
       <c r="C37" t="s">
-        <v>1636</v>
+        <v>2692</v>
       </c>
       <c r="D37" t="s">
-        <v>1637</v>
+        <v>2693</v>
       </c>
       <c r="E37" t="s">
-        <v>1638</v>
+        <v>2694</v>
       </c>
       <c r="F37" t="s">
-        <v>1639</v>
+        <v>2695</v>
       </c>
       <c r="G37" t="s">
-        <v>1640</v>
+        <v>2696</v>
       </c>
       <c r="H37" t="s">
-        <v>1641</v>
+        <v>2697</v>
       </c>
       <c r="I37" t="s">
-        <v>1642</v>
+        <v>2698</v>
       </c>
       <c r="J37" t="s">
-        <v>1643</v>
+        <v>2699</v>
       </c>
       <c r="K37" t="s">
-        <v>1644</v>
+        <v>2700</v>
       </c>
       <c r="L37" t="s">
-        <v>1645</v>
+        <v>2701</v>
       </c>
       <c r="M37">
         <v>77</v>
@@ -9036,7 +13832,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>1646</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -9044,37 +13840,37 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>1647</v>
+        <v>2703</v>
       </c>
       <c r="C38" t="s">
-        <v>1648</v>
+        <v>2704</v>
       </c>
       <c r="D38" t="s">
-        <v>1649</v>
+        <v>2705</v>
       </c>
       <c r="E38" t="s">
-        <v>1650</v>
+        <v>2706</v>
       </c>
       <c r="F38" t="s">
-        <v>1651</v>
+        <v>2707</v>
       </c>
       <c r="G38" t="s">
-        <v>1652</v>
+        <v>2708</v>
       </c>
       <c r="H38" t="s">
-        <v>1653</v>
+        <v>2709</v>
       </c>
       <c r="I38" t="s">
-        <v>1654</v>
+        <v>2710</v>
       </c>
       <c r="J38" t="s">
-        <v>1655</v>
+        <v>2711</v>
       </c>
       <c r="K38" t="s">
-        <v>1656</v>
+        <v>2712</v>
       </c>
       <c r="L38" t="s">
-        <v>1657</v>
+        <v>2713</v>
       </c>
       <c r="M38">
         <v>89</v>
@@ -9100,37 +13896,37 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>1658</v>
+        <v>2714</v>
       </c>
       <c r="C39" t="s">
-        <v>1659</v>
+        <v>2715</v>
       </c>
       <c r="D39" t="s">
-        <v>1660</v>
+        <v>2716</v>
       </c>
       <c r="E39" t="s">
-        <v>1661</v>
+        <v>2717</v>
       </c>
       <c r="F39" t="s">
-        <v>1662</v>
+        <v>2718</v>
       </c>
       <c r="G39" t="s">
-        <v>1663</v>
+        <v>2719</v>
       </c>
       <c r="H39" t="s">
-        <v>1664</v>
+        <v>2720</v>
       </c>
       <c r="I39" t="s">
-        <v>1665</v>
+        <v>2721</v>
       </c>
       <c r="J39" t="s">
-        <v>1666</v>
+        <v>2722</v>
       </c>
       <c r="K39" t="s">
-        <v>1667</v>
+        <v>2723</v>
       </c>
       <c r="L39" t="s">
-        <v>1668</v>
+        <v>2724</v>
       </c>
       <c r="M39">
         <v>23</v>
@@ -9148,7 +13944,7 @@
         <v>13</v>
       </c>
       <c r="R39" t="s">
-        <v>1669</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -9156,37 +13952,37 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>1670</v>
+        <v>2726</v>
       </c>
       <c r="C40" t="s">
-        <v>1671</v>
+        <v>2727</v>
       </c>
       <c r="D40" t="s">
-        <v>1672</v>
+        <v>2728</v>
       </c>
       <c r="E40" t="s">
-        <v>1673</v>
+        <v>2729</v>
       </c>
       <c r="F40" t="s">
-        <v>1674</v>
+        <v>2730</v>
       </c>
       <c r="G40" t="s">
-        <v>1675</v>
+        <v>2731</v>
       </c>
       <c r="H40" t="s">
-        <v>1676</v>
+        <v>2732</v>
       </c>
       <c r="I40" t="s">
-        <v>1677</v>
+        <v>2733</v>
       </c>
       <c r="J40" t="s">
-        <v>1678</v>
+        <v>2734</v>
       </c>
       <c r="K40" t="s">
-        <v>1679</v>
+        <v>2735</v>
       </c>
       <c r="L40" t="s">
-        <v>1680</v>
+        <v>2736</v>
       </c>
       <c r="M40">
         <v>23</v>
@@ -9204,7 +14000,7 @@
         <v>10</v>
       </c>
       <c r="R40" t="s">
-        <v>1681</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -9212,37 +14008,37 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>1682</v>
+        <v>2738</v>
       </c>
       <c r="C41" t="s">
-        <v>1683</v>
+        <v>2739</v>
       </c>
       <c r="D41" t="s">
-        <v>1684</v>
+        <v>2740</v>
       </c>
       <c r="E41" t="s">
-        <v>1685</v>
+        <v>2741</v>
       </c>
       <c r="F41" t="s">
-        <v>1686</v>
+        <v>2742</v>
       </c>
       <c r="G41" t="s">
-        <v>1687</v>
+        <v>2743</v>
       </c>
       <c r="H41" t="s">
-        <v>1688</v>
+        <v>2744</v>
       </c>
       <c r="I41" t="s">
-        <v>1689</v>
+        <v>2745</v>
       </c>
       <c r="J41" t="s">
-        <v>1690</v>
+        <v>2746</v>
       </c>
       <c r="K41" t="s">
-        <v>1691</v>
+        <v>2747</v>
       </c>
       <c r="L41" t="s">
-        <v>1692</v>
+        <v>2748</v>
       </c>
       <c r="M41">
         <v>79</v>
@@ -9260,7 +14056,679 @@
         <v>8</v>
       </c>
       <c r="R41" t="s">
-        <v>1693</v>
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42">
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2750</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2751</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2752</v>
+      </c>
+      <c r="E42" t="s">
+        <v>2753</v>
+      </c>
+      <c r="F42" t="s">
+        <v>2754</v>
+      </c>
+      <c r="G42" t="s">
+        <v>2755</v>
+      </c>
+      <c r="H42" t="s">
+        <v>2756</v>
+      </c>
+      <c r="I42" t="s">
+        <v>2757</v>
+      </c>
+      <c r="J42" t="s">
+        <v>2758</v>
+      </c>
+      <c r="K42" t="s">
+        <v>2759</v>
+      </c>
+      <c r="L42" t="s">
+        <v>2760</v>
+      </c>
+      <c r="M42">
+        <v>79</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>2</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>6</v>
+      </c>
+      <c r="R42" t="s">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2762</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2763</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2764</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2765</v>
+      </c>
+      <c r="F43" t="s">
+        <v>2766</v>
+      </c>
+      <c r="G43" t="s">
+        <v>2767</v>
+      </c>
+      <c r="H43" t="s">
+        <v>2768</v>
+      </c>
+      <c r="I43" t="s">
+        <v>2769</v>
+      </c>
+      <c r="J43" t="s">
+        <v>2770</v>
+      </c>
+      <c r="K43" t="s">
+        <v>2771</v>
+      </c>
+      <c r="L43" t="s">
+        <v>2772</v>
+      </c>
+      <c r="M43">
+        <v>89</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>2</v>
+      </c>
+      <c r="P43">
+        <v>4</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43" t="s">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2776</v>
+      </c>
+      <c r="E44" t="s">
+        <v>2777</v>
+      </c>
+      <c r="F44" t="s">
+        <v>2778</v>
+      </c>
+      <c r="G44" t="s">
+        <v>2779</v>
+      </c>
+      <c r="H44" t="s">
+        <v>2780</v>
+      </c>
+      <c r="I44" t="s">
+        <v>2781</v>
+      </c>
+      <c r="J44" t="s">
+        <v>2782</v>
+      </c>
+      <c r="K44" t="s">
+        <v>2783</v>
+      </c>
+      <c r="L44" t="s">
+        <v>2784</v>
+      </c>
+      <c r="M44">
+        <v>89</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>2</v>
+      </c>
+      <c r="P44">
+        <v>5</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44" t="s">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2786</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2787</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2788</v>
+      </c>
+      <c r="E45" t="s">
+        <v>2789</v>
+      </c>
+      <c r="F45" t="s">
+        <v>2790</v>
+      </c>
+      <c r="G45" t="s">
+        <v>2791</v>
+      </c>
+      <c r="H45" t="s">
+        <v>2792</v>
+      </c>
+      <c r="I45" t="s">
+        <v>2793</v>
+      </c>
+      <c r="J45" t="s">
+        <v>2794</v>
+      </c>
+      <c r="K45" t="s">
+        <v>2795</v>
+      </c>
+      <c r="L45" t="s">
+        <v>2796</v>
+      </c>
+      <c r="M45">
+        <v>89</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>2</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
+      </c>
+      <c r="R45" t="s">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2799</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2800</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2801</v>
+      </c>
+      <c r="F46" t="s">
+        <v>2802</v>
+      </c>
+      <c r="G46" t="s">
+        <v>2803</v>
+      </c>
+      <c r="H46" t="s">
+        <v>2804</v>
+      </c>
+      <c r="I46" t="s">
+        <v>2805</v>
+      </c>
+      <c r="J46" t="s">
+        <v>2806</v>
+      </c>
+      <c r="K46" t="s">
+        <v>2807</v>
+      </c>
+      <c r="L46" t="s">
+        <v>2808</v>
+      </c>
+      <c r="M46">
+        <v>77</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>2</v>
+      </c>
+      <c r="P46">
+        <v>3</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46" t="s">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2811</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2812</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2813</v>
+      </c>
+      <c r="F47" t="s">
+        <v>2814</v>
+      </c>
+      <c r="G47" t="s">
+        <v>2815</v>
+      </c>
+      <c r="H47" t="s">
+        <v>2816</v>
+      </c>
+      <c r="I47" t="s">
+        <v>2817</v>
+      </c>
+      <c r="J47" t="s">
+        <v>2818</v>
+      </c>
+      <c r="K47" t="s">
+        <v>2819</v>
+      </c>
+      <c r="L47" t="s">
+        <v>2820</v>
+      </c>
+      <c r="M47">
+        <v>89</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2822</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2823</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2824</v>
+      </c>
+      <c r="F48" t="s">
+        <v>2825</v>
+      </c>
+      <c r="G48" t="s">
+        <v>2826</v>
+      </c>
+      <c r="H48" t="s">
+        <v>2827</v>
+      </c>
+      <c r="I48" t="s">
+        <v>2828</v>
+      </c>
+      <c r="J48" t="s">
+        <v>2829</v>
+      </c>
+      <c r="K48" t="s">
+        <v>2830</v>
+      </c>
+      <c r="L48" t="s">
+        <v>2831</v>
+      </c>
+      <c r="M48">
+        <v>23</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>2</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>13</v>
+      </c>
+      <c r="R48" t="s">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2833</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2835</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2836</v>
+      </c>
+      <c r="F49" t="s">
+        <v>2837</v>
+      </c>
+      <c r="G49" t="s">
+        <v>2838</v>
+      </c>
+      <c r="H49" t="s">
+        <v>2839</v>
+      </c>
+      <c r="I49" t="s">
+        <v>2840</v>
+      </c>
+      <c r="J49" t="s">
+        <v>2841</v>
+      </c>
+      <c r="K49" t="s">
+        <v>2842</v>
+      </c>
+      <c r="L49" t="s">
+        <v>2843</v>
+      </c>
+      <c r="M49">
+        <v>23</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>2</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>10</v>
+      </c>
+      <c r="R49" t="s">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50">
+        <v>9</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2845</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2846</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2847</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2848</v>
+      </c>
+      <c r="F50" t="s">
+        <v>2849</v>
+      </c>
+      <c r="G50" t="s">
+        <v>2850</v>
+      </c>
+      <c r="H50" t="s">
+        <v>2851</v>
+      </c>
+      <c r="I50" t="s">
+        <v>2852</v>
+      </c>
+      <c r="J50" t="s">
+        <v>2853</v>
+      </c>
+      <c r="K50" t="s">
+        <v>2854</v>
+      </c>
+      <c r="L50" t="s">
+        <v>2855</v>
+      </c>
+      <c r="M50">
+        <v>79</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>2</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>8</v>
+      </c>
+      <c r="R50" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2857</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2858</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2859</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2860</v>
+      </c>
+      <c r="F51" t="s">
+        <v>2861</v>
+      </c>
+      <c r="G51" t="s">
+        <v>2862</v>
+      </c>
+      <c r="H51" t="s">
+        <v>2863</v>
+      </c>
+      <c r="I51" t="s">
+        <v>2864</v>
+      </c>
+      <c r="J51" t="s">
+        <v>2865</v>
+      </c>
+      <c r="K51" t="s">
+        <v>2866</v>
+      </c>
+      <c r="L51" t="s">
+        <v>2867</v>
+      </c>
+      <c r="M51">
+        <v>89</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>2</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>9</v>
+      </c>
+      <c r="R51" t="s">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52">
+        <v>1</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2870</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2871</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2872</v>
+      </c>
+      <c r="F52" t="s">
+        <v>2873</v>
+      </c>
+      <c r="G52" t="s">
+        <v>2874</v>
+      </c>
+      <c r="H52" t="s">
+        <v>2875</v>
+      </c>
+      <c r="I52" t="s">
+        <v>2876</v>
+      </c>
+      <c r="J52" t="s">
+        <v>2877</v>
+      </c>
+      <c r="K52" t="s">
+        <v>2878</v>
+      </c>
+      <c r="L52" t="s">
+        <v>2879</v>
+      </c>
+      <c r="M52">
+        <v>77</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>2</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>32</v>
+      </c>
+      <c r="R52" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53">
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2881</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2884</v>
+      </c>
+      <c r="F53" t="s">
+        <v>2885</v>
+      </c>
+      <c r="G53" t="s">
+        <v>2886</v>
+      </c>
+      <c r="H53" t="s">
+        <v>2887</v>
+      </c>
+      <c r="I53" t="s">
+        <v>2888</v>
+      </c>
+      <c r="J53" t="s">
+        <v>2889</v>
+      </c>
+      <c r="K53" t="s">
+        <v>2890</v>
+      </c>
+      <c r="L53" t="s">
+        <v>2891</v>
+      </c>
+      <c r="M53">
+        <v>77</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>2</v>
+      </c>
+      <c r="P53">
+        <v>3</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53" t="s">
+        <v>2892</v>
       </c>
     </row>
   </sheetData>
